--- a/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T10:05:30+00:00</t>
+    <t>2026-03-13T14:11:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T14:11:35+00:00</t>
+    <t>2026-03-13T17:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:00:40+00:00</t>
+    <t>2026-03-13T17:26:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:39+00:00</t>
+    <t>2026-03-13T17:26:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:16+00:00</t>
+    <t>2026-03-13T22:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.0-snapsnot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T22:26:12+00:00</t>
+    <t>2026-03-20T08:18:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T08:18:16+00:00</t>
+    <t>2026-03-23T13:14:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T13:14:10+00:00</t>
+    <t>2026-03-27T09:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -673,7 +673,7 @@
     <t>fr-lm-corps-document.traitements</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-traitement
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-traitements
 </t>
   </si>
   <si>

--- a/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="204">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -668,16 +668,6 @@
   </si>
   <si>
     <t>Section Traitement à la sortie</t>
-  </si>
-  <si>
-    <t>fr-lm-corps-document.traitementsAdministres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-traitements-administres
-</t>
-  </si>
-  <si>
-    <t>Section Traitements administrés</t>
   </si>
 </sst>
 </file>
@@ -979,7 +969,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ45"/>
+  <dimension ref="A1:AJ44"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.33984375" customWidth="true" bestFit="true"/>
@@ -5429,106 +5419,6 @@
         <v>73</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="C45" s="2"/>
-      <c r="D45" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E45" s="2"/>
-      <c r="F45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I45" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K45" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
-      <c r="P45" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q45" s="2"/>
-      <c r="R45" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S45" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T45" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="AG45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-corps-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
